--- a/tests/lancamentos.xlsx
+++ b/tests/lancamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felipentavares/src/pyo3-cookbook/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C3D04A-ED89-2443-8488-1E974DBAAF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949089F2-0D8B-1147-91B6-5D83ECC16DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11160" yWindow="2020" windowWidth="18080" windowHeight="12220" xr2:uid="{B22E5620-E26D-1E4C-A37E-9FBB7125D6FC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{B22E5620-E26D-1E4C-A37E-9FBB7125D6FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Lançamentos" sheetId="1" r:id="rId1"/>
@@ -124,9 +124,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,7 +489,7 @@
       <c r="C2" s="1">
         <v>46217</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>100</v>
       </c>
     </row>
@@ -502,7 +503,7 @@
       <c r="C3" s="1">
         <v>46217</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>200</v>
       </c>
     </row>
@@ -516,12 +517,13 @@
       <c r="C4" s="1">
         <v>46218</v>
       </c>
-      <c r="D4">
-        <v>50</v>
+      <c r="D4" s="2">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
